--- a/tests/fixtures/xlsx/racesense-regatta.xlsx
+++ b/tests/fixtures/xlsx/racesense-regatta.xlsx
@@ -882,21 +882,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">254</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Checked-In</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">254</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
     </row>
